--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q80_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005279736983809491</v>
+        <v>0.0002373020465702849</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005279736983809491</v>
+        <v>0.0002373020465702849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002451332972009641</v>
+        <v>0.0001500832513649434</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009815754076780425</v>
+        <v>0.0004541678750889304</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009815754076780425</v>
+        <v>0.0004541678750889304</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004091885015888142</v>
+        <v>0.0002465971116683882</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002041323474247078</v>
+        <v>0.0009415253016076081</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002041323474247078</v>
+        <v>0.0009415253016076081</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007812834696572677</v>
+        <v>0.0004894946203059345</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003393852950162665</v>
+        <v>0.001569049274953395</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003393852950162665</v>
+        <v>0.001569049274953395</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001335603294445622</v>
+        <v>0.0007983542731960557</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004098221275492163</v>
+        <v>0.001895315417575855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004098221275492163</v>
+        <v>0.001895315417575855</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001562028586536962</v>
+        <v>0.000960907020986154</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00396714901408023</v>
+        <v>0.001831167291362566</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00396714901408023</v>
+        <v>0.001831167291362566</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001508271519350923</v>
+        <v>0.0009304111871295954</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.003547937869209587</v>
+        <v>0.001638894678082867</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003547937869209587</v>
+        <v>0.001638894678082867</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001362237150635706</v>
+        <v>0.0008365920688797404</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003227970174003399</v>
+        <v>0.001493191723063518</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003227970174003399</v>
+        <v>0.001493191723063518</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001244579970570456</v>
+        <v>0.0007692655357304058</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003132965259561013</v>
+        <v>0.001450956830743231</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003132965259561013</v>
+        <v>0.001450956830743231</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001169035370509727</v>
+        <v>0.0007240893044534307</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002808506025921703</v>
+        <v>0.001303279466034741</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002808506025921703</v>
+        <v>0.001303279466034741</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001128554163021139</v>
+        <v>0.0006795668610714518</v>
       </c>
     </row>
   </sheetData>
